--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="111">
   <si>
     <t>Result</t>
   </si>
@@ -645,6 +645,9 @@
   </si>
   <si>
     <t>Mon Nov 17 22:56:05 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 17 12:14:37 IST 2025</t>
   </si>
 </sst>
 </file>
@@ -2672,10 +2675,10 @@
     </row>
     <row ht="203" r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="150">
   <si>
     <t>Result</t>
   </si>
@@ -648,6 +648,123 @@
   </si>
   <si>
     <t>Wed Dec 17 12:14:37 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:17:23 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:18:35 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:19:48 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:22:13 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:22:55 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:23:32 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:24:46 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:25:21 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:25:56 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:27:16 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:27:54 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:28:35 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:47:08 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:47:42 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:50:20 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:52:56 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:53:32 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:56:26 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:59:06 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:59:45 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:02:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:06:07 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:06:40 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:07:17 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:15:07 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:15:40 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:16:13 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:28:43 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:30:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:40:16 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:41:28 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:43:01 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:44:37 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:47:06 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:48:31 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:39:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:40:27 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 21:41:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 23:23:38 IST 2025</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1222,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1187,7 +1304,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1291,7 +1408,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1414,7 +1531,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1542,7 +1659,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1634,7 +1751,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1724,7 +1841,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1814,7 +1931,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1904,7 +2021,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1994,7 +2111,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2179,7 +2296,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2471,10 +2588,10 @@
     </row>
     <row ht="203" r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2573,10 +2690,10 @@
     </row>
     <row ht="203" r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2678,7 +2795,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2765,7 +2882,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2837,7 +2954,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2912,7 +3029,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -2985,7 +3102,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3060,7 +3177,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3133,7 +3250,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3207,10 +3324,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3240,7 +3357,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3267,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -3340,7 +3457,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3435,7 +3552,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3581,7 +3698,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3721,7 +3838,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3861,7 +3978,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4001,7 +4118,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4141,7 +4258,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>140</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4257,7 +4374,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4373,7 +4490,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4468,7 +4585,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4540,7 +4657,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4612,7 +4729,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4684,7 +4801,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4756,7 +4873,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4828,7 +4945,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="167">
   <si>
     <t>Result</t>
   </si>
@@ -765,6 +765,57 @@
   </si>
   <si>
     <t>Fri Dec 26 23:23:38 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Jan 07 20:07:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 07 20:09:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 21:27:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 21:35:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 21:58:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 21:58:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 22:09:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 22:17:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 22:20:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 22:23:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 22:25:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 22:27:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 08 22:29:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 09 17:04:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 09 18:17:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 09 18:18:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 09 18:19:48 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2588,10 +2639,10 @@
     </row>
     <row ht="203" r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2690,10 +2741,10 @@
     </row>
     <row ht="203" r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2792,10 +2843,10 @@
     </row>
     <row ht="203" r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3324,10 +3375,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3357,7 +3408,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3384,7 +3435,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -4118,7 +4169,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="168">
   <si>
     <t>Result</t>
   </si>
@@ -816,6 +816,9 @@
   </si>
   <si>
     <t>Fri Jan 09 18:19:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jan 12 22:13:10 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1462,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="213">
   <si>
     <t>Result</t>
   </si>
@@ -819,6 +819,141 @@
   </si>
   <si>
     <t>Mon Jan 12 22:13:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 00:58:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 00:59:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:00:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:03:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:04:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:04:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:06:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:06:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:07:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:08:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:09:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:10:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:44:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:44:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:52:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:55:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:56:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:04:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:07:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:07:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:16:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:20:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:20:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:21:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:29:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:29:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:30:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:42:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:43:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:52:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:53:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:55:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:56:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:58:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:59:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 04:05:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 04:06:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 04:07:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 21:12:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 21:18:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 22:43:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 23:08:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 00:25:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 00:27:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 00:28:09 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1273,10 +1408,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1358,7 +1493,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1462,7 +1597,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1585,7 +1720,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1713,7 +1848,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1805,7 +1940,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1895,7 +2030,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1985,7 +2120,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2075,7 +2210,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2165,7 +2300,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2350,7 +2485,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2645,7 +2780,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2747,7 +2882,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2849,7 +2984,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2936,7 +3071,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3008,7 +3143,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3083,7 +3218,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3156,7 +3291,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3231,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>192</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3304,7 +3439,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3381,7 +3516,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3411,7 +3546,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3438,7 +3573,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -3511,7 +3646,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>194</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3606,7 +3741,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3752,7 +3887,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3892,7 +4027,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4032,7 +4167,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4172,7 +4307,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4312,7 +4447,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>197</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4428,7 +4563,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4544,7 +4679,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4639,7 +4774,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4711,7 +4846,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4783,7 +4918,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4855,7 +4990,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4927,7 +5062,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4999,7 +5134,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>206</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="218">
   <si>
     <t>Result</t>
   </si>
@@ -954,6 +954,21 @@
   </si>
   <si>
     <t>Wed Mar 11 00:28:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 21:04:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 21:16:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 21:19:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Mar 13 00:09:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Mar 13 00:16:10 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3741,7 +3756,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="256">
   <si>
     <t>Result</t>
   </si>
@@ -969,6 +969,120 @@
   </si>
   <si>
     <t>Fri Mar 13 00:16:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:06:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:08:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:09:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:11:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:12:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:12:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:14:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:14:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:15:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:16:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:17:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:18:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:36:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:37:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:40:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:42:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:43:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:46:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:48:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:49:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:52:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:55:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:55:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:56:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:03:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:04:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:04:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:15:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:17:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:26:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:27:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:29:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:31:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:34:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:35:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:25:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:26:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 12:26:55 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1423,10 +1537,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1508,7 +1622,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1612,7 +1726,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1735,7 +1849,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1863,7 +1977,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1955,7 +2069,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2045,7 +2159,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2135,7 +2249,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2225,7 +2339,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2315,7 +2429,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2500,7 +2614,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>238</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2795,7 +2909,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2897,7 +3011,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2999,7 +3113,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3086,7 +3200,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3158,7 +3272,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3233,7 +3347,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3306,7 +3420,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3381,7 +3495,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>242</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3454,7 +3568,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3531,7 +3645,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3558,10 +3672,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3588,7 +3702,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -3661,7 +3775,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3756,7 +3870,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3902,7 +4016,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4042,7 +4156,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>249</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4182,7 +4296,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4322,7 +4436,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4462,7 +4576,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4578,7 +4692,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4694,7 +4808,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>252</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4789,7 +4903,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4861,7 +4975,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4933,7 +5047,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5005,7 +5119,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5077,7 +5191,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5149,7 +5263,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="263">
   <si>
     <t>Result</t>
   </si>
@@ -1083,6 +1083,27 @@
   </si>
   <si>
     <t>Tue Jun 02 12:26:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 18:54:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 19:00:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:07:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 20:10:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:19:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:20:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:21:58 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3645,7 +3666,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3672,10 +3693,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3702,7 +3723,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -3870,7 +3891,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4156,7 +4177,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4296,7 +4317,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4436,7 +4457,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="313">
   <si>
     <t>Result</t>
   </si>
@@ -1104,6 +1104,156 @@
   </si>
   <si>
     <t>Fri Jun 05 22:21:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 23:18:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 23:19:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 23:20:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 23:30:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 23:38:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 23:47:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:38:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:39:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:40:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:43:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:44:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:44:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:46:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:47:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:47:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:49:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:49:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:50:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:10:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:11:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:13:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:16:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:17:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:20:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:23:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:24:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:27:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:30:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:31:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:32:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:40:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:41:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:41:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:59:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:01:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:12:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:13:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:15:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:17:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:18:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 02:20:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:14:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:15:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 03:17:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 11:18:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:21:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:22:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:24:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:27:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 12:33:10 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1561,7 +1711,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1643,7 +1793,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1747,7 +1897,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1870,7 +2020,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>272</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -1998,7 +2148,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -2090,7 +2240,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>229</v>
+        <v>280</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2180,7 +2330,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>279</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2270,7 +2420,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2360,7 +2510,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2450,7 +2600,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2635,7 +2785,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2930,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3032,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3134,7 +3284,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3221,7 +3371,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>291</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3293,7 +3443,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3368,7 +3518,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3441,7 +3591,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>290</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3516,7 +3666,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>293</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3589,7 +3739,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3666,7 +3816,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3696,7 +3846,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3723,7 +3873,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>262</v>
+        <v>306</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -3796,7 +3946,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>244</v>
+        <v>295</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3891,7 +4041,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>307</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4037,7 +4187,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>308</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4177,7 +4327,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4317,7 +4467,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>312</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4457,7 +4607,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4597,7 +4747,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>247</v>
+        <v>298</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4713,7 +4863,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>297</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4829,7 +4979,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4924,7 +5074,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>284</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4996,7 +5146,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>286</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5068,7 +5218,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>285</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5140,7 +5290,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5212,7 +5362,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>283</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5284,7 +5434,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>282</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="315">
   <si>
     <t>Result</t>
   </si>
@@ -1254,6 +1254,12 @@
   </si>
   <si>
     <t>Fri Jun 19 12:33:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 23:14:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 00:56:20 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1671,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1707,10 +1713,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>288</v>
       </c>
       <c r="C2" s="3"/>
@@ -1747,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82449780-E031-48D5-B77A-C70DBD60E099}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -1789,10 +1795,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>274</v>
       </c>
       <c r="C2" s="3"/>
@@ -1851,7 +1857,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DC1CCD5-A824-46D1-8E03-288885AFD37A}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -1893,10 +1899,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>273</v>
       </c>
       <c r="C2" s="3"/>
@@ -1935,7 +1941,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A041BDF5-260D-4C88-9BE9-34D621669BA2}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" customWidth="true" width="9.81640625" collapsed="true"/>
@@ -1980,10 +1986,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>62</v>
       </c>
       <c r="C2" s="3"/>
@@ -2016,10 +2022,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>272</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2057,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7731992D-7881-48D0-9061-1E14905AC37D}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="13" max="13" customWidth="true" width="28.36328125" collapsed="true"/>
@@ -2105,10 +2111,10 @@
       </c>
     </row>
     <row ht="188.5" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>61</v>
       </c>
       <c r="C2" s="3"/>
@@ -2144,10 +2150,10 @@
       </c>
     </row>
     <row ht="188.5" r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>278</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2188,7 +2194,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206DC968-58D8-4DD0-BC82-DF0CD0921B92}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="13" max="13" customWidth="true" width="17.1796875" collapsed="true"/>
@@ -2236,10 +2242,10 @@
       </c>
     </row>
     <row ht="261" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>280</v>
       </c>
       <c r="C2" s="3"/>
@@ -2281,7 +2287,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17981BF-ECA3-4B3E-BBE1-4117F8134390}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -2326,10 +2332,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>279</v>
       </c>
       <c r="C2" s="3"/>
@@ -2371,7 +2377,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51944D1B-9B45-4F14-94B4-232A04139A52}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -2416,10 +2422,10 @@
       </c>
     </row>
     <row ht="377" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>276</v>
       </c>
       <c r="C2" s="3"/>
@@ -2461,7 +2467,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125BE5F4-6DCB-4B74-965A-2A1B8749D9E8}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -2506,10 +2512,10 @@
       </c>
     </row>
     <row ht="377" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>277</v>
       </c>
       <c r="C2" s="3"/>
@@ -2551,7 +2557,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0885A1C1-EAD3-4FBD-9595-596BAA6EA611}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -2596,10 +2602,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>275</v>
       </c>
       <c r="C2" s="3"/>
@@ -2641,7 +2647,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C0D33A-2EC8-4BF6-B54B-4E680640D2E6}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="29.1796875" collapsed="true"/>
@@ -2745,7 +2751,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A814AFF7-515F-465B-94F7-1ECECB99CB8C}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2781,10 +2787,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>289</v>
       </c>
       <c r="C2" s="3"/>
@@ -2817,7 +2823,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418C9335-5599-4DF8-B9E1-DC0D08A18354}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="22.453125" collapsed="true"/>
@@ -2921,7 +2927,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E68741B-6F05-455D-9A92-FE831FDDA104}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="29.90625" collapsed="true"/>
@@ -3025,7 +3031,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626903B0-5C9F-484A-9B05-1DD0B9C0F68E}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -3076,10 +3082,10 @@
       </c>
     </row>
     <row ht="203" r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>271</v>
       </c>
       <c r="C2" s="3"/>
@@ -3127,7 +3133,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3FAD2F-9501-4262-B6DA-9C1FC4650EB6}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -3178,10 +3184,10 @@
       </c>
     </row>
     <row ht="203" r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>270</v>
       </c>
       <c r="C2" s="3"/>
@@ -3229,7 +3235,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38FF3975-D7A9-43F6-BD06-BA179809991B}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -3280,11 +3286,11 @@
       </c>
     </row>
     <row ht="203" r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>269</v>
+      <c r="A2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>314</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3331,7 +3337,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E02F51-555B-49C2-8C54-78632D6874FA}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -3367,10 +3373,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>291</v>
       </c>
       <c r="C2" s="3"/>
@@ -3403,7 +3409,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37C3328-39C9-41FD-9DB4-ADF86208FC39}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -3439,10 +3445,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>292</v>
       </c>
       <c r="C2" s="3"/>
@@ -3475,7 +3481,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C3A691B-8A11-403A-A18C-0B3D16CACD43}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -3514,10 +3520,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>294</v>
       </c>
       <c r="C2" s="3"/>
@@ -3551,7 +3557,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37656D7C-21ED-46B0-BCCF-CB4452FF881C}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -3587,10 +3593,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>290</v>
       </c>
       <c r="C2" s="3"/>
@@ -3623,7 +3629,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFDC152B-B1BC-4655-9345-694EE576670D}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -3662,10 +3668,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>293</v>
       </c>
       <c r="C2" s="3"/>
@@ -3699,7 +3705,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDEF0D9-E05F-45C5-8D9F-25228B1275D2}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -3735,10 +3741,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>287</v>
       </c>
       <c r="C2" s="3"/>
@@ -3771,7 +3777,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6039023C-1CA6-42DC-810C-1BD4192BEEFE}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
@@ -3801,21 +3807,21 @@
       <c r="G1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>304</v>
       </c>
       <c r="C2" s="14"/>
@@ -3828,24 +3834,24 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f xml:space="preserve"> "Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H2" t="str" s="0">
         <f xml:space="preserve"> "InstallmentPlan"</f>
         <v>InstallmentPlan</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I2" t="str" s="0">
         <f xml:space="preserve"> "Daily"</f>
         <v>Daily</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>305</v>
       </c>
       <c r="D3" s="12" t="s">
@@ -3857,22 +3863,22 @@
       <c r="F3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" t="str" s="0">
         <f ref="G3:G4" si="0" t="shared" xml:space="preserve"> "Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>306</v>
       </c>
       <c r="D4" s="12" t="s">
@@ -3884,11 +3890,11 @@
       <c r="F4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G4" t="str" s="0">
         <f si="0" t="shared"/>
         <v>Carlos</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="0">
         <v>44</v>
       </c>
     </row>
@@ -3900,7 +3906,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57CC2B03-4328-41F8-892F-CD81F2306003}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="30.36328125" collapsed="true"/>
@@ -3942,10 +3948,10 @@
       </c>
     </row>
     <row ht="159.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>295</v>
       </c>
       <c r="C2" s="3"/>
@@ -3979,7 +3985,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55622C3-FD59-462E-B48B-E29C12630952}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="9" max="9" bestFit="true" customWidth="true" width="20.453125" collapsed="true"/>
@@ -4008,13 +4014,13 @@
       <c r="G1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>47</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4037,10 +4043,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>307</v>
       </c>
       <c r="C2" s="14"/>
@@ -4053,17 +4059,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>49</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4123,7 +4129,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2219A53-CA02-4D9A-9DD5-DA00AC5C4A23}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="10" max="10" bestFit="true" customWidth="true" width="20.90625" collapsed="true"/>
@@ -4154,13 +4160,13 @@
       <c r="G1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>47</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4183,10 +4189,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>308</v>
       </c>
       <c r="C2" s="14"/>
@@ -4199,17 +4205,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>53</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4269,7 +4275,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61DCC56-CE37-4DAE-9D92-37CB9C481C7F}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -4294,13 +4300,13 @@
       <c r="G1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>47</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4323,10 +4329,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>309</v>
       </c>
       <c r="C2" s="14"/>
@@ -4339,17 +4345,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>53</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4409,7 +4415,7 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811FF27C-D0FF-4DEB-9DD7-F2E87A7294CB}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -4434,13 +4440,13 @@
       <c r="G1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>47</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4463,10 +4469,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>312</v>
       </c>
       <c r="C2" s="14"/>
@@ -4479,17 +4485,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>53</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4549,7 +4555,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D06A526-F613-4F63-B541-7FF18EFD935D}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -4574,13 +4580,13 @@
       <c r="G1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>47</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4603,10 +4609,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>301</v>
       </c>
       <c r="C2" s="14"/>
@@ -4619,17 +4625,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>53</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4689,7 +4695,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02109C6A-9E4E-4705-AE64-D5133AE96048}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -4714,13 +4720,13 @@
       <c r="G1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>47</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4743,10 +4749,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>298</v>
       </c>
       <c r="C2" s="14"/>
@@ -4759,17 +4765,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>53</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4802,7 +4808,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7CE9CCC-95AD-4B48-9052-C4AAA33A463F}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="27.7265625" collapsed="true"/>
@@ -4830,13 +4836,13 @@
       <c r="G1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>47</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4859,10 +4865,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>297</v>
       </c>
       <c r="C2" s="14"/>
@@ -4875,17 +4881,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>53</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -4918,7 +4924,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DEB38C-C9EF-4355-A944-36732259D0F6}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="25.6328125" collapsed="true"/>
@@ -4946,13 +4952,13 @@
       <c r="G1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>47</v>
       </c>
       <c r="K1" s="4" t="s">
@@ -4975,10 +4981,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>311</v>
       </c>
       <c r="C2" s="14"/>
@@ -4991,17 +4997,17 @@
       <c r="F2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>53</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -5034,7 +5040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A973579-5DFF-4678-B07A-68B908946F3C}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -5070,10 +5076,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>284</v>
       </c>
       <c r="C2" s="3"/>
@@ -5106,7 +5112,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFFBF56E-14AC-4995-9D06-ECEAEC4D7822}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -5142,10 +5148,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>286</v>
       </c>
       <c r="C2" s="3"/>
@@ -5178,7 +5184,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5A0D3B4-E6B2-45F0-8319-7F7FECCF3BD4}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -5214,10 +5220,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>285</v>
       </c>
       <c r="C2" s="3"/>
@@ -5250,7 +5256,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{777701B4-BB5E-43A1-B36C-41C7E1286146}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -5286,10 +5292,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>281</v>
       </c>
       <c r="C2" s="3"/>
@@ -5322,7 +5328,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382225BB-FBC4-4803-99D7-28B6A923E6A2}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -5358,10 +5364,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>283</v>
       </c>
       <c r="C2" s="3"/>
@@ -5394,7 +5400,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B8D28A0-6595-433A-95CB-C2AAB29F36D2}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -5430,10 +5436,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>282</v>
       </c>
       <c r="C2" s="3"/>

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="377">
   <si>
     <t>Result</t>
   </si>
@@ -1260,6 +1260,192 @@
   </si>
   <si>
     <t>Fri Jul 03 00:56:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:36:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:37:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:38:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:40:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:41:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:41:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:42:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:43:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:43:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:44:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:45:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:45:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:04:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:04:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:07:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:10:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:10:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:13:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:16:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:16:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:19:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:23:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:24:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:24:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:17:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:18:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:19:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:21:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:22:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:22:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:23:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:24:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:24:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:25:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:25:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:26:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:44:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:44:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:47:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:49:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:50:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:53:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:55:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:56:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:58:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 01:02:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 01:02:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 01:03:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:30:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:31:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:31:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:41:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:42:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:52:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:53:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:55:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:57:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:58:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:59:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:42:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:43:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 20:44:36 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1717,7 +1903,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>288</v>
+        <v>358</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1799,7 +1985,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>274</v>
+        <v>344</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1903,7 +2089,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>273</v>
+        <v>343</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2026,7 +2212,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>272</v>
+        <v>342</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -2154,7 +2340,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>278</v>
+        <v>348</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -2246,7 +2432,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2336,7 +2522,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>279</v>
+        <v>349</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2426,7 +2612,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>276</v>
+        <v>346</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2516,7 +2702,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>277</v>
+        <v>347</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2606,7 +2792,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>275</v>
+        <v>345</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2791,7 +2977,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>289</v>
+        <v>359</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3086,7 +3272,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>271</v>
+        <v>341</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3188,7 +3374,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3287,10 +3473,10 @@
     </row>
     <row ht="203" r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3377,7 +3563,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>291</v>
+        <v>361</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3449,7 +3635,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3524,7 +3710,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>294</v>
+        <v>364</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3597,7 +3783,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3672,7 +3858,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>293</v>
+        <v>363</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3745,7 +3931,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>287</v>
+        <v>357</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3822,7 +4008,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3849,10 +4035,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>305</v>
+        <v>375</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3879,7 +4065,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>306</v>
+        <v>376</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -3952,7 +4138,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -4047,7 +4233,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>307</v>
+        <v>366</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4193,7 +4379,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4333,7 +4519,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>309</v>
+        <v>370</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4473,7 +4659,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>312</v>
+        <v>372</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4613,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4753,7 +4939,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>298</v>
+        <v>368</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4869,7 +5055,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>297</v>
+        <v>367</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4985,7 +5171,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>311</v>
+        <v>373</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -5080,7 +5266,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>284</v>
+        <v>354</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5152,7 +5338,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>286</v>
+        <v>356</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5224,7 +5410,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>285</v>
+        <v>355</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5296,7 +5482,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>281</v>
+        <v>351</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5368,7 +5554,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>283</v>
+        <v>353</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5440,7 +5626,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>282</v>
+        <v>352</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="415">
   <si>
     <t>Result</t>
   </si>
@@ -1446,6 +1446,120 @@
   </si>
   <si>
     <t>Sat Aug 08 20:44:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:14:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:15:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:16:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:18:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:18:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:19:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:20:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:20:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:20:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:21:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:22:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:22:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:40:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:41:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:43:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:46:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:46:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:49:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:52:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:52:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:55:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:59:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:59:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:59:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:44:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:44:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:45:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:53:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:55:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:03:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:03:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:05:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:06:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:07:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:09:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:48:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:49:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:50:37 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1903,7 +2017,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1985,7 +2099,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2089,7 +2203,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2212,7 +2326,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -2340,7 +2454,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -2432,7 +2546,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2522,7 +2636,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>349</v>
+        <v>387</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2612,7 +2726,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2702,7 +2816,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2792,7 +2906,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2977,7 +3091,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3272,7 +3386,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3374,7 +3488,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3476,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3563,7 +3677,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3635,7 +3749,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3710,7 +3824,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3783,7 +3897,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3858,7 +3972,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>363</v>
+        <v>401</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3931,7 +4045,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4005,10 +4119,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>374</v>
+        <v>412</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4038,7 +4152,7 @@
         <v>16</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>375</v>
+        <v>413</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -4065,7 +4179,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>376</v>
+        <v>414</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -4138,7 +4252,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -4233,7 +4347,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4379,7 +4493,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4519,7 +4633,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4659,7 +4773,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>372</v>
+        <v>410</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4799,7 +4913,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4939,7 +5053,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -5055,7 +5169,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -5171,7 +5285,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>373</v>
+        <v>411</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -5266,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5338,7 +5452,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5410,7 +5524,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5482,7 +5596,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5554,7 +5668,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5626,7 +5740,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
